--- a/StructureDefinition-heartland-remote-monitoring-observation.xlsx
+++ b/StructureDefinition-heartland-remote-monitoring-observation.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-remote-monitoring-observation</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-remote-monitoring-observation</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,7 +686,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-monitoring-observation-code-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-monitoring-observation-code-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -710,7 +710,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://heartlandprotocol.org/fhir/StructureDefinition/heartland-patient|Patient)
+    <t xml:space="preserve">Reference(https://fhir.heartlandprotocol.org/StructureDefinition/heartland-patient|Patient)
 </t>
   </si>
   <si>
@@ -1803,7 +1803,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.27734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.1015625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
